--- a/jogos_2025-07-08.xlsx
+++ b/jogos_2025-07-08.xlsx
@@ -813,7 +813,7 @@
         <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="Z2">
         <v>1.47</v>
@@ -828,22 +828,22 @@
         <v>1.5</v>
       </c>
       <c r="AD2">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE2">
         <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG2">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AH2">
         <v>8.9</v>
       </c>
       <c r="AI2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ2" t="s">
         <v>62</v>
@@ -852,13 +852,13 @@
         <v>62</v>
       </c>
       <c r="AL2">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AM2">
         <v>1.32</v>
       </c>
       <c r="AN2">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AO2">
         <v>-1</v>
@@ -867,31 +867,31 @@
         <v>1.2</v>
       </c>
       <c r="AQ2">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AS2">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AT2">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AU2">
         <v>4</v>
       </c>
       <c r="AV2">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AW2">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AX2">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AY2">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AZ2">
         <v>0</v>

--- a/jogos_2025-07-08.xlsx
+++ b/jogos_2025-07-08.xlsx
@@ -792,7 +792,7 @@
         <v>3</v>
       </c>
       <c r="R2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S2">
         <v>2.4</v>
@@ -801,19 +801,19 @@
         <v>3.4</v>
       </c>
       <c r="U2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V2">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="W2">
         <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y2">
-        <v>7</v>
+        <v>6.76</v>
       </c>
       <c r="Z2">
         <v>1.47</v>
@@ -834,16 +834,16 @@
         <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG2">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AH2">
-        <v>8.9</v>
+        <v>9.75</v>
       </c>
       <c r="AI2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="s">
         <v>62</v>
@@ -852,7 +852,7 @@
         <v>62</v>
       </c>
       <c r="AL2">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AM2">
         <v>1.32</v>
@@ -864,34 +864,34 @@
         <v>-1</v>
       </c>
       <c r="AP2">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR2">
         <v>1.77</v>
       </c>
       <c r="AS2">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AT2">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AU2">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="AV2">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AW2">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="AX2">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AY2">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AZ2">
         <v>0</v>

--- a/jogos_2025-07-08.xlsx
+++ b/jogos_2025-07-08.xlsx
@@ -792,34 +792,34 @@
         <v>3</v>
       </c>
       <c r="R2">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="S2">
+        <v>2.35</v>
+      </c>
+      <c r="T2">
+        <v>3.3</v>
+      </c>
+      <c r="U2">
+        <v>1.26</v>
+      </c>
+      <c r="V2">
+        <v>8.6</v>
+      </c>
+      <c r="W2">
+        <v>1.02</v>
+      </c>
+      <c r="X2">
+        <v>1.06</v>
+      </c>
+      <c r="Y2">
+        <v>6.91</v>
+      </c>
+      <c r="Z2">
+        <v>1.5</v>
+      </c>
+      <c r="AA2">
         <v>2.4</v>
-      </c>
-      <c r="T2">
-        <v>3.4</v>
-      </c>
-      <c r="U2">
-        <v>1.29</v>
-      </c>
-      <c r="V2">
-        <v>9.75</v>
-      </c>
-      <c r="W2">
-        <v>1.03</v>
-      </c>
-      <c r="X2">
-        <v>1.1</v>
-      </c>
-      <c r="Y2">
-        <v>6.76</v>
-      </c>
-      <c r="Z2">
-        <v>1.47</v>
-      </c>
-      <c r="AA2">
-        <v>2.55</v>
       </c>
       <c r="AB2">
         <v>2.3</v>
@@ -828,22 +828,22 @@
         <v>1.5</v>
       </c>
       <c r="AD2">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF2">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG2">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AH2">
-        <v>9.75</v>
+        <v>11</v>
       </c>
       <c r="AI2">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ2" t="s">
         <v>62</v>
@@ -852,46 +852,46 @@
         <v>62</v>
       </c>
       <c r="AL2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AM2">
         <v>1.32</v>
       </c>
       <c r="AN2">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AO2">
         <v>-1</v>
       </c>
       <c r="AP2">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AQ2">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AR2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AS2">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AT2">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AU2">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="AV2">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AW2">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AX2">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AY2">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AZ2">
         <v>0</v>

--- a/jogos_2025-07-08.xlsx
+++ b/jogos_2025-07-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -199,10 +145,13 @@
     <t>Criciúma</t>
   </si>
   <si>
-    <t>incomplete</t>
-  </si>
-  <si>
-    <t>[]</t>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['4']</t>
   </si>
 </sst>
 </file>
@@ -566,10 +515,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD2"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -684,103 +633,49 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45846</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="L2">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="M2">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O2">
         <v>1.57</v>
@@ -792,120 +687,66 @@
         <v>3</v>
       </c>
       <c r="R2">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S2">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="T2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U2">
         <v>1.26</v>
       </c>
       <c r="V2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>6.91</v>
+        <v>6.5</v>
       </c>
       <c r="Z2">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AA2">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AB2">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC2">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AD2">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AE2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG2">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH2">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ2" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AL2">
-        <v>1.33</v>
-      </c>
-      <c r="AM2">
-        <v>1.32</v>
-      </c>
-      <c r="AN2">
-        <v>1.99</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>1.12</v>
-      </c>
-      <c r="AQ2">
-        <v>1.31</v>
-      </c>
-      <c r="AR2">
-        <v>1.78</v>
-      </c>
-      <c r="AS2">
-        <v>1.94</v>
-      </c>
-      <c r="AT2">
-        <v>2.47</v>
-      </c>
-      <c r="AU2">
-        <v>4.42</v>
-      </c>
-      <c r="AV2">
-        <v>2.97</v>
-      </c>
-      <c r="AW2">
-        <v>2.21</v>
-      </c>
-      <c r="AX2">
-        <v>1.76</v>
-      </c>
-      <c r="AY2">
-        <v>1.46</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.57</v>
-      </c>
-      <c r="BC2">
-        <v>3</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>45</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45846.8125</v>
       </c>
     </row>

--- a/jogos_2025-07-08.xlsx
+++ b/jogos_2025-07-08.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Artsakh</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.71</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA3" t="n">
         <v>3.7</v>
       </c>
-      <c r="N3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '58', '70']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.08</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45846.54166666666</v>
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Artsakh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="O4" t="n">
-        <v>6</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AI4" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['8', '58', '70']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>1.36</v>
+        <v>4.33</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45846.54166666666</v>
@@ -1288,16 +1288,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T7" t="n">
         <v>3.75</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45846.625</v>
@@ -1417,16 +1417,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="P8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>3</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45846.625</v>
@@ -1675,109 +1675,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Virtus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.95</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3.25</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AD10" t="n">
         <v>1.33</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '78']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>8.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.49</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.91</v>
+        <v>7.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45846.66666666666</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Virtus</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>2.95</v>
       </c>
       <c r="M11" t="n">
-        <v>13</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>21</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="U11" t="n">
         <v>1.33</v>
       </c>
-      <c r="R11" t="n">
+      <c r="V11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.22</v>
       </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AC11" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['45', '78']</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
-        <v>8.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>1.49</v>
       </c>
       <c r="AI11" t="n">
-        <v>7.5</v>
+        <v>1.91</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45846.66666666666</v>
